--- a/output/yearly_population_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_62_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5472</v>
+        <v>4643</v>
       </c>
       <c r="C2" t="n">
-        <v>10487</v>
+        <v>10160</v>
       </c>
       <c r="D2" t="n">
-        <v>19122</v>
+        <v>21215</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3124</v>
+        <v>2595</v>
       </c>
       <c r="C3" t="n">
-        <v>2577</v>
+        <v>4461</v>
       </c>
       <c r="D3" t="n">
-        <v>10002</v>
+        <v>12664</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2535</v>
+        <v>2292</v>
       </c>
       <c r="C4" t="n">
-        <v>3641</v>
+        <v>5345</v>
       </c>
       <c r="D4" t="n">
-        <v>5130</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1776</v>
+        <v>1542</v>
       </c>
       <c r="C5" t="n">
-        <v>3976</v>
+        <v>4465</v>
       </c>
       <c r="D5" t="n">
-        <v>2165</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1058</v>
+        <v>900</v>
       </c>
       <c r="C6" t="n">
-        <v>2924</v>
+        <v>2982</v>
       </c>
       <c r="D6" t="n">
-        <v>1027</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="C7" t="n">
-        <v>1728</v>
+        <v>1841</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>789</v>
+        <v>969</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8191</v>
+        <v>6309</v>
       </c>
       <c r="C2" t="n">
-        <v>11743</v>
+        <v>9101</v>
       </c>
       <c r="D2" t="n">
-        <v>17365</v>
+        <v>19792</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3416</v>
+        <v>2842</v>
       </c>
       <c r="C3" t="n">
-        <v>5550</v>
+        <v>6243</v>
       </c>
       <c r="D3" t="n">
-        <v>10627</v>
+        <v>12975</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2423</v>
+        <v>2080</v>
       </c>
       <c r="C4" t="n">
-        <v>2999</v>
+        <v>4801</v>
       </c>
       <c r="D4" t="n">
-        <v>5815</v>
+        <v>7171</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1875</v>
+        <v>1655</v>
       </c>
       <c r="C5" t="n">
-        <v>3729</v>
+        <v>4743</v>
       </c>
       <c r="D5" t="n">
-        <v>2562</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1259</v>
+        <v>1085</v>
       </c>
       <c r="C6" t="n">
-        <v>3360</v>
+        <v>3635</v>
       </c>
       <c r="D6" t="n">
-        <v>1198</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>687</v>
+        <v>559</v>
       </c>
       <c r="C7" t="n">
-        <v>2289</v>
+        <v>2336</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="C8" t="n">
-        <v>1204</v>
+        <v>1353</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>645</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9476</v>
+        <v>5860</v>
       </c>
       <c r="C2" t="n">
-        <v>7651</v>
+        <v>8632</v>
       </c>
       <c r="D2" t="n">
-        <v>21310</v>
+        <v>20682</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4367</v>
+        <v>3445</v>
       </c>
       <c r="C3" t="n">
-        <v>7279</v>
+        <v>6598</v>
       </c>
       <c r="D3" t="n">
-        <v>10792</v>
+        <v>12996</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2423</v>
+        <v>2043</v>
       </c>
       <c r="C4" t="n">
-        <v>4083</v>
+        <v>5351</v>
       </c>
       <c r="D4" t="n">
-        <v>6321</v>
+        <v>7844</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1879</v>
+        <v>1652</v>
       </c>
       <c r="C5" t="n">
-        <v>3322</v>
+        <v>4623</v>
       </c>
       <c r="D5" t="n">
-        <v>2983</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1402</v>
+        <v>1202</v>
       </c>
       <c r="C6" t="n">
-        <v>3454</v>
+        <v>4069</v>
       </c>
       <c r="D6" t="n">
-        <v>1366</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>831</v>
+        <v>691</v>
       </c>
       <c r="C7" t="n">
-        <v>2727</v>
+        <v>2846</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>321</v>
       </c>
       <c r="C8" t="n">
-        <v>1660</v>
+        <v>1734</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="C9" t="n">
-        <v>804</v>
+        <v>922</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>426</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
         <v>208</v>
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>5428</v>
       </c>
       <c r="C2" t="n">
-        <v>5019</v>
+        <v>5800</v>
       </c>
       <c r="D2" t="n">
-        <v>17188</v>
+        <v>17044</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4929</v>
+        <v>3941</v>
       </c>
       <c r="C3" t="n">
-        <v>9657</v>
+        <v>9545</v>
       </c>
       <c r="D3" t="n">
-        <v>12101</v>
+        <v>14311</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1736</v>
+        <v>1526</v>
       </c>
       <c r="C4" t="n">
-        <v>5540</v>
+        <v>7468</v>
       </c>
       <c r="D4" t="n">
-        <v>6220</v>
+        <v>7606</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1295</v>
+        <v>1110</v>
       </c>
       <c r="C5" t="n">
-        <v>3384</v>
+        <v>3987</v>
       </c>
       <c r="D5" t="n">
-        <v>2169</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>767</v>
+        <v>638</v>
       </c>
       <c r="C6" t="n">
-        <v>2672</v>
+        <v>2789</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>296</v>
       </c>
       <c r="C7" t="n">
-        <v>1626</v>
+        <v>1699</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>787</v>
+        <v>903</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
         <v>203</v>
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>161</v>
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4918</v>
+        <v>3426</v>
       </c>
       <c r="C2" t="n">
-        <v>2315</v>
+        <v>3140</v>
       </c>
       <c r="D2" t="n">
-        <v>11730</v>
+        <v>11933</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5525</v>
+        <v>3962</v>
       </c>
       <c r="C3" t="n">
-        <v>6710</v>
+        <v>7086</v>
       </c>
       <c r="D3" t="n">
-        <v>12233</v>
+        <v>13858</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2591</v>
+        <v>2137</v>
       </c>
       <c r="C4" t="n">
-        <v>7653</v>
+        <v>8504</v>
       </c>
       <c r="D4" t="n">
-        <v>6993</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1416</v>
+        <v>1220</v>
       </c>
       <c r="C5" t="n">
-        <v>4407</v>
+        <v>5565</v>
       </c>
       <c r="D5" t="n">
-        <v>2689</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>922</v>
+        <v>763</v>
       </c>
       <c r="C6" t="n">
-        <v>3067</v>
+        <v>3384</v>
       </c>
       <c r="D6" t="n">
-        <v>907</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>2076</v>
+        <v>2130</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1057</v>
+        <v>1177</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2184,7 +2184,7 @@
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5829</v>
+        <v>3409</v>
       </c>
       <c r="C2" t="n">
-        <v>5553</v>
+        <v>9020</v>
       </c>
       <c r="D2" t="n">
-        <v>15617</v>
+        <v>13513</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4406</v>
+        <v>3163</v>
       </c>
       <c r="C3" t="n">
-        <v>3963</v>
+        <v>4596</v>
       </c>
       <c r="D3" t="n">
-        <v>11318</v>
+        <v>12627</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3373</v>
+        <v>2510</v>
       </c>
       <c r="C4" t="n">
-        <v>7078</v>
+        <v>7619</v>
       </c>
       <c r="D4" t="n">
-        <v>7685</v>
+        <v>9207</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1716</v>
+        <v>1438</v>
       </c>
       <c r="C5" t="n">
-        <v>5904</v>
+        <v>6859</v>
       </c>
       <c r="D5" t="n">
-        <v>3309</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1059</v>
+        <v>889</v>
       </c>
       <c r="C6" t="n">
-        <v>3696</v>
+        <v>4388</v>
       </c>
       <c r="D6" t="n">
-        <v>1168</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>512</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>2521</v>
+        <v>2703</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>1506</v>
+        <v>1580</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>691</v>
+        <v>747</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3361</v>
+        <v>1993</v>
       </c>
       <c r="C2" t="n">
-        <v>2495</v>
+        <v>4179</v>
       </c>
       <c r="D2" t="n">
-        <v>10773</v>
+        <v>9377</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4598</v>
+        <v>3108</v>
       </c>
       <c r="C3" t="n">
-        <v>4395</v>
+        <v>5970</v>
       </c>
       <c r="D3" t="n">
-        <v>11527</v>
+        <v>12423</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3759</v>
+        <v>2795</v>
       </c>
       <c r="C4" t="n">
-        <v>6503</v>
+        <v>7176</v>
       </c>
       <c r="D4" t="n">
-        <v>8169</v>
+        <v>9697</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1828</v>
+        <v>1528</v>
       </c>
       <c r="C5" t="n">
-        <v>7021</v>
+        <v>7977</v>
       </c>
       <c r="D5" t="n">
-        <v>3586</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>751</v>
       </c>
       <c r="C6" t="n">
-        <v>4708</v>
+        <v>5410</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>2703</v>
+        <v>2880</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1178</v>
+        <v>1227</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3774</v>
+        <v>2296</v>
       </c>
       <c r="C2" t="n">
-        <v>5285</v>
+        <v>8165</v>
       </c>
       <c r="D2" t="n">
-        <v>16438</v>
+        <v>9339</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3467</v>
+        <v>2258</v>
       </c>
       <c r="C3" t="n">
-        <v>3083</v>
+        <v>4570</v>
       </c>
       <c r="D3" t="n">
-        <v>10736</v>
+        <v>11173</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3591</v>
+        <v>2559</v>
       </c>
       <c r="C4" t="n">
-        <v>5377</v>
+        <v>6447</v>
       </c>
       <c r="D4" t="n">
-        <v>8468</v>
+        <v>9847</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2331</v>
+        <v>1841</v>
       </c>
       <c r="C5" t="n">
-        <v>6698</v>
+        <v>7518</v>
       </c>
       <c r="D5" t="n">
-        <v>4180</v>
+        <v>4951</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1179</v>
+        <v>951</v>
       </c>
       <c r="C6" t="n">
-        <v>5730</v>
+        <v>6521</v>
       </c>
       <c r="D6" t="n">
-        <v>1495</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>3599</v>
+        <v>3976</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1783</v>
+        <v>1866</v>
       </c>
       <c r="D8" t="n">
         <v>407</v>
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="D9" t="n">
         <v>300</v>
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D13" t="n">
         <v>62</v>
-      </c>
-      <c r="D13" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>46</v>
+      </c>
+      <c r="D14" t="n">
         <v>47</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2752</v>
+        <v>1548</v>
       </c>
       <c r="C2" t="n">
-        <v>3835</v>
+        <v>4162</v>
       </c>
       <c r="D2" t="n">
-        <v>11965</v>
+        <v>7083</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3125</v>
+        <v>1988</v>
       </c>
       <c r="C3" t="n">
-        <v>3614</v>
+        <v>5505</v>
       </c>
       <c r="D3" t="n">
-        <v>10864</v>
+        <v>10345</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3239</v>
+        <v>2275</v>
       </c>
       <c r="C4" t="n">
-        <v>4429</v>
+        <v>5723</v>
       </c>
       <c r="D4" t="n">
-        <v>8699</v>
+        <v>9820</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2595</v>
+        <v>1964</v>
       </c>
       <c r="C5" t="n">
-        <v>6308</v>
+        <v>7187</v>
       </c>
       <c r="D5" t="n">
-        <v>4587</v>
+        <v>5459</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1400</v>
+        <v>1126</v>
       </c>
       <c r="C6" t="n">
-        <v>6285</v>
+        <v>7110</v>
       </c>
       <c r="D6" t="n">
-        <v>1778</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>274</v>
       </c>
       <c r="C7" t="n">
-        <v>4408</v>
+        <v>4895</v>
       </c>
       <c r="D7" t="n">
-        <v>722</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2271</v>
+        <v>2406</v>
       </c>
       <c r="D8" t="n">
         <v>430</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5033</v>
+        <v>3043</v>
       </c>
       <c r="C2" t="n">
-        <v>5335</v>
+        <v>7275</v>
       </c>
       <c r="D2" t="n">
-        <v>20158</v>
+        <v>12564</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2509</v>
+        <v>1537</v>
       </c>
       <c r="C3" t="n">
-        <v>3280</v>
+        <v>4404</v>
       </c>
       <c r="D3" t="n">
-        <v>10292</v>
+        <v>9291</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>1905</v>
       </c>
       <c r="C4" t="n">
-        <v>3969</v>
+        <v>5509</v>
       </c>
       <c r="D4" t="n">
-        <v>8767</v>
+        <v>9597</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2599</v>
+        <v>1893</v>
       </c>
       <c r="C5" t="n">
-        <v>5365</v>
+        <v>6433</v>
       </c>
       <c r="D5" t="n">
-        <v>5039</v>
+        <v>5826</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1696</v>
+        <v>1319</v>
       </c>
       <c r="C6" t="n">
-        <v>6237</v>
+        <v>7079</v>
       </c>
       <c r="D6" t="n">
-        <v>2132</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>636</v>
+        <v>489</v>
       </c>
       <c r="C7" t="n">
-        <v>5203</v>
+        <v>5739</v>
       </c>
       <c r="D7" t="n">
-        <v>849</v>
+        <v>891</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>3065</v>
+        <v>3331</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1295</v>
+        <v>1308</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5144</v>
+        <v>4368</v>
       </c>
       <c r="C2" t="n">
-        <v>5665</v>
+        <v>8974</v>
       </c>
       <c r="D2" t="n">
-        <v>5865</v>
+        <v>11805</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3520</v>
+        <v>2175</v>
       </c>
       <c r="C2" t="n">
-        <v>2945</v>
+        <v>4132</v>
       </c>
       <c r="D2" t="n">
-        <v>14836</v>
+        <v>9247</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3512</v>
+        <v>2177</v>
       </c>
       <c r="C3" t="n">
-        <v>4062</v>
+        <v>5450</v>
       </c>
       <c r="D3" t="n">
-        <v>11675</v>
+        <v>10368</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3795</v>
+        <v>2719</v>
       </c>
       <c r="C4" t="n">
-        <v>5764</v>
+        <v>7729</v>
       </c>
       <c r="D4" t="n">
-        <v>9072</v>
+        <v>9910</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1687</v>
+        <v>1271</v>
       </c>
       <c r="C5" t="n">
-        <v>8372</v>
+        <v>9680</v>
       </c>
       <c r="D5" t="n">
-        <v>4700</v>
+        <v>5432</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>587</v>
+        <v>451</v>
       </c>
       <c r="C6" t="n">
-        <v>6443</v>
+        <v>7081</v>
       </c>
       <c r="D6" t="n">
-        <v>1781</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="7">
@@ -4271,10 +4271,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>3003</v>
+        <v>3264</v>
       </c>
       <c r="D7" t="n">
         <v>566</v>
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1269</v>
+        <v>1281</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7581</v>
+        <v>5842</v>
       </c>
       <c r="C2" t="n">
-        <v>5082</v>
+        <v>5656</v>
       </c>
       <c r="D2" t="n">
-        <v>7524</v>
+        <v>13985</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2186</v>
+        <v>1857</v>
       </c>
       <c r="C3" t="n">
-        <v>2900</v>
+        <v>4522</v>
       </c>
       <c r="D3" t="n">
-        <v>1671</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5037</v>
+        <v>3824</v>
       </c>
       <c r="C2" t="n">
-        <v>5664</v>
+        <v>4678</v>
       </c>
       <c r="D2" t="n">
-        <v>18249</v>
+        <v>15236</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4005</v>
+        <v>3158</v>
       </c>
       <c r="C3" t="n">
-        <v>3578</v>
+        <v>4453</v>
       </c>
       <c r="D3" t="n">
-        <v>2531</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>983</v>
+        <v>841</v>
       </c>
       <c r="C4" t="n">
-        <v>1769</v>
+        <v>2693</v>
       </c>
       <c r="D4" t="n">
-        <v>1518</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5037</v>
+        <v>5528</v>
       </c>
       <c r="C2" t="n">
-        <v>8377</v>
+        <v>5818</v>
       </c>
       <c r="D2" t="n">
-        <v>20301</v>
+        <v>18873</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3714</v>
+        <v>2871</v>
       </c>
       <c r="C3" t="n">
-        <v>4081</v>
+        <v>3960</v>
       </c>
       <c r="D3" t="n">
-        <v>4863</v>
+        <v>5769</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2107</v>
+        <v>1690</v>
       </c>
       <c r="C4" t="n">
-        <v>2739</v>
+        <v>3633</v>
       </c>
       <c r="D4" t="n">
-        <v>1666</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>464</v>
+        <v>406</v>
       </c>
       <c r="C5" t="n">
-        <v>1077</v>
+        <v>1569</v>
       </c>
       <c r="D5" t="n">
-        <v>1199</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
         <v>148</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4946</v>
+        <v>4660</v>
       </c>
       <c r="C2" t="n">
-        <v>5603</v>
+        <v>8512</v>
       </c>
       <c r="D2" t="n">
-        <v>16188</v>
+        <v>24336</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>3374</v>
       </c>
       <c r="C3" t="n">
-        <v>5504</v>
+        <v>4279</v>
       </c>
       <c r="D3" t="n">
-        <v>6867</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>1941</v>
       </c>
       <c r="C4" t="n">
-        <v>3416</v>
+        <v>3698</v>
       </c>
       <c r="D4" t="n">
-        <v>2182</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1065</v>
+        <v>858</v>
       </c>
       <c r="C5" t="n">
-        <v>1932</v>
+        <v>2626</v>
       </c>
       <c r="D5" t="n">
-        <v>1247</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>690</v>
+        <v>942</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5690</v>
+        <v>4908</v>
       </c>
       <c r="C2" t="n">
-        <v>6282</v>
+        <v>9096</v>
       </c>
       <c r="D2" t="n">
-        <v>16621</v>
+        <v>23707</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3100</v>
+        <v>2911</v>
       </c>
       <c r="C3" t="n">
-        <v>4547</v>
+        <v>5277</v>
       </c>
       <c r="D3" t="n">
-        <v>7338</v>
+        <v>8859</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1883</v>
+        <v>1636</v>
       </c>
       <c r="C4" t="n">
-        <v>3762</v>
+        <v>3263</v>
       </c>
       <c r="D4" t="n">
-        <v>2574</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>916</v>
+        <v>729</v>
       </c>
       <c r="C5" t="n">
-        <v>1972</v>
+        <v>2330</v>
       </c>
       <c r="D5" t="n">
-        <v>1118</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>895</v>
+        <v>1206</v>
       </c>
       <c r="D6" t="n">
-        <v>752</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>333</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4597</v>
+        <v>4305</v>
       </c>
       <c r="C2" t="n">
-        <v>2763</v>
+        <v>6165</v>
       </c>
       <c r="D2" t="n">
-        <v>18109</v>
+        <v>25220</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3673</v>
+        <v>3246</v>
       </c>
       <c r="C3" t="n">
-        <v>4794</v>
+        <v>6480</v>
       </c>
       <c r="D3" t="n">
-        <v>8419</v>
+        <v>10806</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2196</v>
+        <v>1983</v>
       </c>
       <c r="C4" t="n">
-        <v>4173</v>
+        <v>4432</v>
       </c>
       <c r="D4" t="n">
-        <v>3501</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1248</v>
+        <v>1061</v>
       </c>
       <c r="C5" t="n">
-        <v>3013</v>
+        <v>2836</v>
       </c>
       <c r="D5" t="n">
-        <v>1366</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>580</v>
+        <v>463</v>
       </c>
       <c r="C6" t="n">
-        <v>1514</v>
+        <v>1838</v>
       </c>
       <c r="D6" t="n">
-        <v>814</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>657</v>
+        <v>860</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4178</v>
+        <v>3138</v>
       </c>
       <c r="C2" t="n">
-        <v>2808</v>
+        <v>4778</v>
       </c>
       <c r="D2" t="n">
-        <v>17581</v>
+        <v>20220</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3440</v>
+        <v>3132</v>
       </c>
       <c r="C3" t="n">
-        <v>3143</v>
+        <v>5460</v>
       </c>
       <c r="D3" t="n">
-        <v>9427</v>
+        <v>12334</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2518</v>
+        <v>2233</v>
       </c>
       <c r="C4" t="n">
-        <v>4449</v>
+        <v>5457</v>
       </c>
       <c r="D4" t="n">
-        <v>4386</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1527</v>
+        <v>1340</v>
       </c>
       <c r="C5" t="n">
-        <v>3607</v>
+        <v>3665</v>
       </c>
       <c r="D5" t="n">
-        <v>1734</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>831</v>
+        <v>686</v>
       </c>
       <c r="C6" t="n">
-        <v>2316</v>
+        <v>2353</v>
       </c>
       <c r="D6" t="n">
-        <v>895</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>1118</v>
+        <v>1377</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>474</v>
+        <v>593</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_62_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4643</v>
+        <v>5749</v>
       </c>
       <c r="C2" t="n">
-        <v>10160</v>
+        <v>13449</v>
       </c>
       <c r="D2" t="n">
-        <v>21215</v>
+        <v>35025</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2595</v>
+        <v>3240</v>
       </c>
       <c r="C3" t="n">
-        <v>4461</v>
+        <v>8939</v>
       </c>
       <c r="D3" t="n">
-        <v>12664</v>
+        <v>14741</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2292</v>
+        <v>2509</v>
       </c>
       <c r="C4" t="n">
-        <v>5345</v>
+        <v>5862</v>
       </c>
       <c r="D4" t="n">
-        <v>6406</v>
+        <v>7332</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1542</v>
+        <v>1624</v>
       </c>
       <c r="C5" t="n">
-        <v>4465</v>
+        <v>4272</v>
       </c>
       <c r="D5" t="n">
-        <v>2511</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>900</v>
+        <v>947</v>
       </c>
       <c r="C6" t="n">
-        <v>2982</v>
+        <v>3186</v>
       </c>
       <c r="D6" t="n">
-        <v>1142</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>1841</v>
+        <v>1966</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>969</v>
+        <v>876</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>77</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6309</v>
+        <v>6025</v>
       </c>
       <c r="C2" t="n">
-        <v>9101</v>
+        <v>12668</v>
       </c>
       <c r="D2" t="n">
-        <v>19792</v>
+        <v>37576</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2842</v>
+        <v>3514</v>
       </c>
       <c r="C3" t="n">
-        <v>6243</v>
+        <v>9648</v>
       </c>
       <c r="D3" t="n">
-        <v>12975</v>
+        <v>16509</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2080</v>
+        <v>2414</v>
       </c>
       <c r="C4" t="n">
-        <v>4801</v>
+        <v>7131</v>
       </c>
       <c r="D4" t="n">
-        <v>7171</v>
+        <v>8318</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1655</v>
+        <v>1785</v>
       </c>
       <c r="C5" t="n">
-        <v>4743</v>
+        <v>4915</v>
       </c>
       <c r="D5" t="n">
-        <v>3070</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1085</v>
+        <v>1121</v>
       </c>
       <c r="C6" t="n">
-        <v>3635</v>
+        <v>3603</v>
       </c>
       <c r="D6" t="n">
-        <v>1325</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="C7" t="n">
-        <v>2336</v>
+        <v>2503</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C8" t="n">
-        <v>1353</v>
+        <v>1326</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>566</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5860</v>
+        <v>6053</v>
       </c>
       <c r="C2" t="n">
-        <v>8632</v>
+        <v>19558</v>
       </c>
       <c r="D2" t="n">
-        <v>20682</v>
+        <v>42487</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3445</v>
+        <v>3669</v>
       </c>
       <c r="C3" t="n">
-        <v>6598</v>
+        <v>9645</v>
       </c>
       <c r="D3" t="n">
-        <v>12996</v>
+        <v>17980</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2043</v>
+        <v>2424</v>
       </c>
       <c r="C4" t="n">
-        <v>5351</v>
+        <v>7977</v>
       </c>
       <c r="D4" t="n">
-        <v>7844</v>
+        <v>9164</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1652</v>
+        <v>1812</v>
       </c>
       <c r="C5" t="n">
-        <v>4623</v>
+        <v>5680</v>
       </c>
       <c r="D5" t="n">
-        <v>3537</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1202</v>
+        <v>1271</v>
       </c>
       <c r="C6" t="n">
-        <v>4069</v>
+        <v>4100</v>
       </c>
       <c r="D6" t="n">
-        <v>1558</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="C7" t="n">
-        <v>2846</v>
+        <v>2908</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C8" t="n">
-        <v>1734</v>
+        <v>1762</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>922</v>
+        <v>848</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5428</v>
+        <v>5693</v>
       </c>
       <c r="C2" t="n">
-        <v>5800</v>
+        <v>13612</v>
       </c>
       <c r="D2" t="n">
-        <v>17044</v>
+        <v>34852</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3941</v>
+        <v>4347</v>
       </c>
       <c r="C3" t="n">
-        <v>9545</v>
+        <v>14662</v>
       </c>
       <c r="D3" t="n">
-        <v>14311</v>
+        <v>19212</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1526</v>
+        <v>1674</v>
       </c>
       <c r="C4" t="n">
-        <v>7468</v>
+        <v>9741</v>
       </c>
       <c r="D4" t="n">
-        <v>7606</v>
+        <v>8869</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1110</v>
+        <v>1174</v>
       </c>
       <c r="C5" t="n">
-        <v>3987</v>
+        <v>4018</v>
       </c>
       <c r="D5" t="n">
-        <v>2511</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="C6" t="n">
-        <v>2789</v>
+        <v>2849</v>
       </c>
       <c r="D6" t="n">
-        <v>775</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>1699</v>
+        <v>1726</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>903</v>
+        <v>831</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>161</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3426</v>
+        <v>3511</v>
       </c>
       <c r="C2" t="n">
-        <v>3140</v>
+        <v>6422</v>
       </c>
       <c r="D2" t="n">
-        <v>11933</v>
+        <v>24693</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3962</v>
+        <v>4257</v>
       </c>
       <c r="C3" t="n">
-        <v>7086</v>
+        <v>12904</v>
       </c>
       <c r="D3" t="n">
-        <v>13858</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2137</v>
+        <v>2306</v>
       </c>
       <c r="C4" t="n">
-        <v>8504</v>
+        <v>12132</v>
       </c>
       <c r="D4" t="n">
-        <v>8550</v>
+        <v>10173</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1220</v>
+        <v>1296</v>
       </c>
       <c r="C5" t="n">
-        <v>5565</v>
+        <v>6341</v>
       </c>
       <c r="D5" t="n">
-        <v>3118</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C6" t="n">
-        <v>3384</v>
+        <v>3416</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>2130</v>
+        <v>2146</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>1177</v>
+        <v>1100</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>392</v>
       </c>
       <c r="D9" t="n">
         <v>257</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3409</v>
+        <v>3357</v>
       </c>
       <c r="C2" t="n">
-        <v>9020</v>
+        <v>6971</v>
       </c>
       <c r="D2" t="n">
-        <v>13513</v>
+        <v>20236</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3163</v>
+        <v>3327</v>
       </c>
       <c r="C3" t="n">
-        <v>4596</v>
+        <v>8886</v>
       </c>
       <c r="D3" t="n">
-        <v>12627</v>
+        <v>19625</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2510</v>
+        <v>2688</v>
       </c>
       <c r="C4" t="n">
-        <v>7619</v>
+        <v>12242</v>
       </c>
       <c r="D4" t="n">
-        <v>9207</v>
+        <v>11535</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1438</v>
+        <v>1517</v>
       </c>
       <c r="C5" t="n">
-        <v>6859</v>
+        <v>8822</v>
       </c>
       <c r="D5" t="n">
-        <v>3909</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="C6" t="n">
-        <v>4388</v>
+        <v>4680</v>
       </c>
       <c r="D6" t="n">
-        <v>1273</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C7" t="n">
-        <v>2703</v>
+        <v>2667</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>1580</v>
+        <v>1520</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>747</v>
+        <v>656</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>134</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1993</v>
+        <v>2036</v>
       </c>
       <c r="C2" t="n">
-        <v>4179</v>
+        <v>3407</v>
       </c>
       <c r="D2" t="n">
-        <v>9377</v>
+        <v>14117</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3108</v>
+        <v>3219</v>
       </c>
       <c r="C3" t="n">
-        <v>5970</v>
+        <v>8031</v>
       </c>
       <c r="D3" t="n">
-        <v>12423</v>
+        <v>19248</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2795</v>
+        <v>2938</v>
       </c>
       <c r="C4" t="n">
-        <v>7176</v>
+        <v>12131</v>
       </c>
       <c r="D4" t="n">
-        <v>9697</v>
+        <v>12523</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1528</v>
+        <v>1573</v>
       </c>
       <c r="C5" t="n">
-        <v>7977</v>
+        <v>10932</v>
       </c>
       <c r="D5" t="n">
-        <v>4243</v>
+        <v>4732</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>751</v>
+        <v>727</v>
       </c>
       <c r="C6" t="n">
-        <v>5410</v>
+        <v>5388</v>
       </c>
       <c r="D6" t="n">
-        <v>1246</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>2880</v>
+        <v>2756</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1227</v>
+        <v>1074</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>131</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>96</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2296</v>
+        <v>2572</v>
       </c>
       <c r="C2" t="n">
-        <v>8165</v>
+        <v>9568</v>
       </c>
       <c r="D2" t="n">
-        <v>9339</v>
+        <v>17949</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2258</v>
+        <v>2363</v>
       </c>
       <c r="C3" t="n">
-        <v>4570</v>
+        <v>5367</v>
       </c>
       <c r="D3" t="n">
-        <v>11173</v>
+        <v>17328</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2559</v>
+        <v>2691</v>
       </c>
       <c r="C4" t="n">
-        <v>6447</v>
+        <v>10145</v>
       </c>
       <c r="D4" t="n">
-        <v>9847</v>
+        <v>13175</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C5" t="n">
-        <v>7518</v>
+        <v>11316</v>
       </c>
       <c r="D5" t="n">
-        <v>4951</v>
+        <v>5755</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="C6" t="n">
-        <v>6521</v>
+        <v>7576</v>
       </c>
       <c r="D6" t="n">
-        <v>1673</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>3976</v>
+        <v>3789</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1866</v>
+        <v>1655</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>630</v>
+        <v>513</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1548</v>
+        <v>1747</v>
       </c>
       <c r="C2" t="n">
-        <v>4162</v>
+        <v>5683</v>
       </c>
       <c r="D2" t="n">
-        <v>7083</v>
+        <v>13419</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1988</v>
+        <v>2128</v>
       </c>
       <c r="C3" t="n">
-        <v>5505</v>
+        <v>6357</v>
       </c>
       <c r="D3" t="n">
-        <v>10345</v>
+        <v>16482</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2275</v>
+        <v>2377</v>
       </c>
       <c r="C4" t="n">
-        <v>5723</v>
+        <v>8437</v>
       </c>
       <c r="D4" t="n">
-        <v>9820</v>
+        <v>13545</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1964</v>
+        <v>1991</v>
       </c>
       <c r="C5" t="n">
-        <v>7187</v>
+        <v>11024</v>
       </c>
       <c r="D5" t="n">
-        <v>5459</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1126</v>
+        <v>1062</v>
       </c>
       <c r="C6" t="n">
-        <v>7110</v>
+        <v>8941</v>
       </c>
       <c r="D6" t="n">
-        <v>1968</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>4895</v>
+        <v>4863</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2406</v>
+        <v>2107</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>549</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3043</v>
+        <v>1967</v>
       </c>
       <c r="C2" t="n">
-        <v>7275</v>
+        <v>8697</v>
       </c>
       <c r="D2" t="n">
-        <v>12564</v>
+        <v>18921</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1537</v>
+        <v>1689</v>
       </c>
       <c r="C3" t="n">
-        <v>4404</v>
+        <v>5464</v>
       </c>
       <c r="D3" t="n">
-        <v>9291</v>
+        <v>15110</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1905</v>
+        <v>1995</v>
       </c>
       <c r="C4" t="n">
-        <v>5509</v>
+        <v>7442</v>
       </c>
       <c r="D4" t="n">
-        <v>9597</v>
+        <v>13527</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1893</v>
+        <v>1952</v>
       </c>
       <c r="C5" t="n">
-        <v>6433</v>
+        <v>9826</v>
       </c>
       <c r="D5" t="n">
-        <v>5826</v>
+        <v>7052</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1319</v>
+        <v>1241</v>
       </c>
       <c r="C6" t="n">
-        <v>7079</v>
+        <v>9611</v>
       </c>
       <c r="D6" t="n">
-        <v>2411</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>422</v>
       </c>
       <c r="C7" t="n">
-        <v>5739</v>
+        <v>6259</v>
       </c>
       <c r="D7" t="n">
-        <v>891</v>
+        <v>882</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>3331</v>
+        <v>3018</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1308</v>
+        <v>1006</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4368</v>
+        <v>4294</v>
       </c>
       <c r="C2" t="n">
-        <v>8974</v>
+        <v>5229</v>
       </c>
       <c r="D2" t="n">
-        <v>11805</v>
+        <v>15489</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2175</v>
+        <v>1453</v>
       </c>
       <c r="C2" t="n">
-        <v>4132</v>
+        <v>5219</v>
       </c>
       <c r="D2" t="n">
-        <v>9247</v>
+        <v>14228</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2177</v>
+        <v>2261</v>
       </c>
       <c r="C3" t="n">
-        <v>5450</v>
+        <v>6760</v>
       </c>
       <c r="D3" t="n">
-        <v>10368</v>
+        <v>16452</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2719</v>
+        <v>2806</v>
       </c>
       <c r="C4" t="n">
-        <v>7729</v>
+        <v>10764</v>
       </c>
       <c r="D4" t="n">
-        <v>9910</v>
+        <v>13707</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1271</v>
+        <v>1146</v>
       </c>
       <c r="C5" t="n">
-        <v>9680</v>
+        <v>13854</v>
       </c>
       <c r="D5" t="n">
-        <v>5432</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="C6" t="n">
-        <v>7081</v>
+        <v>7735</v>
       </c>
       <c r="D6" t="n">
-        <v>1941</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>3264</v>
+        <v>2957</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1281</v>
+        <v>985</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
         <v>134</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5842</v>
+        <v>6805</v>
       </c>
       <c r="C2" t="n">
-        <v>5656</v>
+        <v>8471</v>
       </c>
       <c r="D2" t="n">
-        <v>13985</v>
+        <v>18250</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1857</v>
+        <v>1826</v>
       </c>
       <c r="C3" t="n">
-        <v>4522</v>
+        <v>2635</v>
       </c>
       <c r="D3" t="n">
-        <v>2622</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3824</v>
+        <v>5093</v>
       </c>
       <c r="C2" t="n">
-        <v>4678</v>
+        <v>8937</v>
       </c>
       <c r="D2" t="n">
-        <v>15236</v>
+        <v>28083</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3158</v>
+        <v>3538</v>
       </c>
       <c r="C3" t="n">
-        <v>4453</v>
+        <v>5120</v>
       </c>
       <c r="D3" t="n">
-        <v>4338</v>
+        <v>5523</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>841</v>
+        <v>827</v>
       </c>
       <c r="C4" t="n">
-        <v>2693</v>
+        <v>1589</v>
       </c>
       <c r="D4" t="n">
-        <v>1709</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5528</v>
+        <v>4578</v>
       </c>
       <c r="C2" t="n">
-        <v>5818</v>
+        <v>5455</v>
       </c>
       <c r="D2" t="n">
-        <v>18873</v>
+        <v>25691</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2871</v>
+        <v>3533</v>
       </c>
       <c r="C3" t="n">
-        <v>3960</v>
+        <v>6233</v>
       </c>
       <c r="D3" t="n">
-        <v>5769</v>
+        <v>8734</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1690</v>
+        <v>1850</v>
       </c>
       <c r="C4" t="n">
-        <v>3633</v>
+        <v>3555</v>
       </c>
       <c r="D4" t="n">
-        <v>2161</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="C5" t="n">
-        <v>1569</v>
+        <v>964</v>
       </c>
       <c r="D5" t="n">
-        <v>1233</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5280,7 +5280,7 @@
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4660</v>
+        <v>4949</v>
       </c>
       <c r="C2" t="n">
-        <v>8512</v>
+        <v>5447</v>
       </c>
       <c r="D2" t="n">
-        <v>24336</v>
+        <v>22163</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3374</v>
+        <v>3346</v>
       </c>
       <c r="C3" t="n">
-        <v>4279</v>
+        <v>5076</v>
       </c>
       <c r="D3" t="n">
-        <v>7354</v>
+        <v>10696</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1941</v>
+        <v>2251</v>
       </c>
       <c r="C4" t="n">
-        <v>3698</v>
+        <v>4920</v>
       </c>
       <c r="D4" t="n">
-        <v>2753</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>858</v>
+        <v>912</v>
       </c>
       <c r="C5" t="n">
-        <v>2626</v>
+        <v>2287</v>
       </c>
       <c r="D5" t="n">
-        <v>1344</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C6" t="n">
-        <v>942</v>
+        <v>627</v>
       </c>
       <c r="D6" t="n">
         <v>957</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4908</v>
+        <v>5082</v>
       </c>
       <c r="C2" t="n">
-        <v>9096</v>
+        <v>8561</v>
       </c>
       <c r="D2" t="n">
-        <v>23707</v>
+        <v>21318</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2911</v>
+        <v>3000</v>
       </c>
       <c r="C3" t="n">
-        <v>5277</v>
+        <v>4313</v>
       </c>
       <c r="D3" t="n">
-        <v>8859</v>
+        <v>10995</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1636</v>
+        <v>1725</v>
       </c>
       <c r="C4" t="n">
-        <v>3263</v>
+        <v>4100</v>
       </c>
       <c r="D4" t="n">
-        <v>3037</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>729</v>
+        <v>824</v>
       </c>
       <c r="C5" t="n">
-        <v>2330</v>
+        <v>2655</v>
       </c>
       <c r="D5" t="n">
-        <v>1265</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>1206</v>
+        <v>985</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>312</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4305</v>
+        <v>5556</v>
       </c>
       <c r="C2" t="n">
-        <v>6165</v>
+        <v>9629</v>
       </c>
       <c r="D2" t="n">
-        <v>25220</v>
+        <v>24274</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3246</v>
+        <v>3356</v>
       </c>
       <c r="C3" t="n">
-        <v>6480</v>
+        <v>5846</v>
       </c>
       <c r="D3" t="n">
-        <v>10806</v>
+        <v>11920</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1983</v>
+        <v>2074</v>
       </c>
       <c r="C4" t="n">
-        <v>4432</v>
+        <v>4143</v>
       </c>
       <c r="D4" t="n">
-        <v>4174</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1061</v>
+        <v>1137</v>
       </c>
       <c r="C5" t="n">
-        <v>2836</v>
+        <v>3445</v>
       </c>
       <c r="D5" t="n">
-        <v>1583</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="C6" t="n">
-        <v>1838</v>
+        <v>1909</v>
       </c>
       <c r="D6" t="n">
-        <v>852</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>860</v>
+        <v>694</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
         <v>280</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3138</v>
+        <v>4269</v>
       </c>
       <c r="C2" t="n">
-        <v>4778</v>
+        <v>13696</v>
       </c>
       <c r="D2" t="n">
-        <v>20220</v>
+        <v>31096</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3132</v>
+        <v>3636</v>
       </c>
       <c r="C3" t="n">
-        <v>5460</v>
+        <v>6845</v>
       </c>
       <c r="D3" t="n">
-        <v>12334</v>
+        <v>13038</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2233</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>5457</v>
+        <v>5021</v>
       </c>
       <c r="D4" t="n">
-        <v>5280</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1340</v>
+        <v>1397</v>
       </c>
       <c r="C5" t="n">
-        <v>3665</v>
+        <v>3755</v>
       </c>
       <c r="D5" t="n">
-        <v>2032</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>686</v>
+        <v>743</v>
       </c>
       <c r="C6" t="n">
-        <v>2353</v>
+        <v>2698</v>
       </c>
       <c r="D6" t="n">
-        <v>973</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C7" t="n">
-        <v>1377</v>
+        <v>1317</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>593</v>
+        <v>486</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
         <v>294</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_62_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5749</v>
+        <v>1128</v>
       </c>
       <c r="C2" t="n">
-        <v>13449</v>
+        <v>2603</v>
       </c>
       <c r="D2" t="n">
-        <v>35025</v>
+        <v>10789</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3240</v>
+        <v>1976</v>
       </c>
       <c r="C3" t="n">
-        <v>8939</v>
+        <v>8166</v>
       </c>
       <c r="D3" t="n">
-        <v>14741</v>
+        <v>9772</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2509</v>
+        <v>1391</v>
       </c>
       <c r="C4" t="n">
-        <v>5862</v>
+        <v>9529</v>
       </c>
       <c r="D4" t="n">
-        <v>7332</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1624</v>
+        <v>763</v>
       </c>
       <c r="C5" t="n">
-        <v>4272</v>
+        <v>4590</v>
       </c>
       <c r="D5" t="n">
-        <v>3079</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>947</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>3186</v>
+        <v>1615</v>
       </c>
       <c r="D6" t="n">
-        <v>1271</v>
+        <v>738</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>1966</v>
+        <v>591</v>
       </c>
       <c r="D7" t="n">
-        <v>678</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>876</v>
+        <v>334</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6025</v>
+        <v>1047</v>
       </c>
       <c r="C2" t="n">
-        <v>12668</v>
+        <v>6844</v>
       </c>
       <c r="D2" t="n">
-        <v>37576</v>
+        <v>16946</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3514</v>
+        <v>1325</v>
       </c>
       <c r="C3" t="n">
-        <v>9648</v>
+        <v>4521</v>
       </c>
       <c r="D3" t="n">
-        <v>16509</v>
+        <v>9324</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2414</v>
+        <v>1454</v>
       </c>
       <c r="C4" t="n">
-        <v>7131</v>
+        <v>8663</v>
       </c>
       <c r="D4" t="n">
-        <v>8318</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1785</v>
+        <v>937</v>
       </c>
       <c r="C5" t="n">
-        <v>4915</v>
+        <v>7102</v>
       </c>
       <c r="D5" t="n">
-        <v>3609</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1121</v>
+        <v>479</v>
       </c>
       <c r="C6" t="n">
-        <v>3603</v>
+        <v>3126</v>
       </c>
       <c r="D6" t="n">
-        <v>1531</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>585</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>2503</v>
+        <v>1098</v>
       </c>
       <c r="D7" t="n">
-        <v>751</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1326</v>
+        <v>458</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>566</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6053</v>
+        <v>555</v>
       </c>
       <c r="C2" t="n">
-        <v>19558</v>
+        <v>2830</v>
       </c>
       <c r="D2" t="n">
-        <v>42487</v>
+        <v>11424</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3669</v>
+        <v>1196</v>
       </c>
       <c r="C3" t="n">
-        <v>9645</v>
+        <v>5200</v>
       </c>
       <c r="D3" t="n">
-        <v>17980</v>
+        <v>10046</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2424</v>
+        <v>1594</v>
       </c>
       <c r="C4" t="n">
-        <v>7977</v>
+        <v>7727</v>
       </c>
       <c r="D4" t="n">
-        <v>9164</v>
+        <v>5704</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1812</v>
+        <v>961</v>
       </c>
       <c r="C5" t="n">
-        <v>5680</v>
+        <v>8411</v>
       </c>
       <c r="D5" t="n">
-        <v>4177</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1271</v>
+        <v>380</v>
       </c>
       <c r="C6" t="n">
-        <v>4100</v>
+        <v>4161</v>
       </c>
       <c r="D6" t="n">
-        <v>1775</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>709</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>2908</v>
+        <v>1079</v>
       </c>
       <c r="D7" t="n">
-        <v>850</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>328</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1762</v>
+        <v>471</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>848</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>366</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5693</v>
+        <v>1083</v>
       </c>
       <c r="C2" t="n">
-        <v>13612</v>
+        <v>4460</v>
       </c>
       <c r="D2" t="n">
-        <v>34852</v>
+        <v>9054</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4347</v>
+        <v>764</v>
       </c>
       <c r="C3" t="n">
-        <v>14662</v>
+        <v>3486</v>
       </c>
       <c r="D3" t="n">
-        <v>19212</v>
+        <v>9548</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1674</v>
+        <v>1259</v>
       </c>
       <c r="C4" t="n">
-        <v>9741</v>
+        <v>6281</v>
       </c>
       <c r="D4" t="n">
-        <v>8869</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1174</v>
+        <v>1125</v>
       </c>
       <c r="C5" t="n">
-        <v>4018</v>
+        <v>8049</v>
       </c>
       <c r="D5" t="n">
-        <v>2862</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>655</v>
+        <v>561</v>
       </c>
       <c r="C6" t="n">
-        <v>2849</v>
+        <v>6158</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>1726</v>
+        <v>2489</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>831</v>
+        <v>734</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3511</v>
+        <v>698</v>
       </c>
       <c r="C2" t="n">
-        <v>6422</v>
+        <v>2517</v>
       </c>
       <c r="D2" t="n">
-        <v>24693</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4257</v>
+        <v>771</v>
       </c>
       <c r="C3" t="n">
-        <v>12904</v>
+        <v>3526</v>
       </c>
       <c r="D3" t="n">
-        <v>20416</v>
+        <v>8930</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2306</v>
+        <v>1006</v>
       </c>
       <c r="C4" t="n">
-        <v>12132</v>
+        <v>5016</v>
       </c>
       <c r="D4" t="n">
-        <v>10173</v>
+        <v>6731</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1296</v>
+        <v>1152</v>
       </c>
       <c r="C5" t="n">
-        <v>6341</v>
+        <v>7443</v>
       </c>
       <c r="D5" t="n">
-        <v>3607</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>768</v>
+        <v>685</v>
       </c>
       <c r="C6" t="n">
-        <v>3416</v>
+        <v>7160</v>
       </c>
       <c r="D6" t="n">
-        <v>1022</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>2146</v>
+        <v>3737</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1100</v>
+        <v>1159</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>433</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3357</v>
+        <v>760</v>
       </c>
       <c r="C2" t="n">
-        <v>6971</v>
+        <v>6216</v>
       </c>
       <c r="D2" t="n">
-        <v>20236</v>
+        <v>9192</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3327</v>
+        <v>622</v>
       </c>
       <c r="C3" t="n">
-        <v>8886</v>
+        <v>2685</v>
       </c>
       <c r="D3" t="n">
-        <v>19625</v>
+        <v>8067</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2688</v>
+        <v>792</v>
       </c>
       <c r="C4" t="n">
-        <v>12242</v>
+        <v>4230</v>
       </c>
       <c r="D4" t="n">
-        <v>11535</v>
+        <v>6885</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1517</v>
+        <v>1015</v>
       </c>
       <c r="C5" t="n">
-        <v>8822</v>
+        <v>6169</v>
       </c>
       <c r="D5" t="n">
-        <v>4505</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>896</v>
+        <v>807</v>
       </c>
       <c r="C6" t="n">
-        <v>4680</v>
+        <v>7216</v>
       </c>
       <c r="D6" t="n">
-        <v>1380</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>2667</v>
+        <v>5248</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>1520</v>
+        <v>2205</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>656</v>
+        <v>707</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2036</v>
+        <v>510</v>
       </c>
       <c r="C2" t="n">
-        <v>3407</v>
+        <v>3233</v>
       </c>
       <c r="D2" t="n">
-        <v>14117</v>
+        <v>6618</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3219</v>
+        <v>843</v>
       </c>
       <c r="C3" t="n">
-        <v>8031</v>
+        <v>3879</v>
       </c>
       <c r="D3" t="n">
-        <v>19248</v>
+        <v>8810</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2938</v>
+        <v>1321</v>
       </c>
       <c r="C4" t="n">
-        <v>12131</v>
+        <v>6097</v>
       </c>
       <c r="D4" t="n">
-        <v>12523</v>
+        <v>7097</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1573</v>
+        <v>820</v>
       </c>
       <c r="C5" t="n">
-        <v>10932</v>
+        <v>9626</v>
       </c>
       <c r="D5" t="n">
-        <v>4732</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>5388</v>
+        <v>6910</v>
       </c>
       <c r="D6" t="n">
-        <v>1333</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>2756</v>
+        <v>2160</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1074</v>
+        <v>692</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2572</v>
+        <v>277</v>
       </c>
       <c r="C2" t="n">
-        <v>9568</v>
+        <v>3150</v>
       </c>
       <c r="D2" t="n">
-        <v>17949</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2363</v>
+        <v>590</v>
       </c>
       <c r="C3" t="n">
-        <v>5367</v>
+        <v>3126</v>
       </c>
       <c r="D3" t="n">
-        <v>17328</v>
+        <v>7862</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2691</v>
+        <v>920</v>
       </c>
       <c r="C4" t="n">
-        <v>10145</v>
+        <v>4691</v>
       </c>
       <c r="D4" t="n">
-        <v>13175</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1843</v>
+        <v>745</v>
       </c>
       <c r="C5" t="n">
-        <v>11316</v>
+        <v>7053</v>
       </c>
       <c r="D5" t="n">
-        <v>5755</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>939</v>
+        <v>295</v>
       </c>
       <c r="C6" t="n">
-        <v>7576</v>
+        <v>6653</v>
       </c>
       <c r="D6" t="n">
-        <v>1740</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>3789</v>
+        <v>3047</v>
       </c>
       <c r="D7" t="n">
-        <v>670</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1655</v>
+        <v>814</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>513</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>133</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1747</v>
+        <v>462</v>
       </c>
       <c r="C2" t="n">
-        <v>5683</v>
+        <v>3527</v>
       </c>
       <c r="D2" t="n">
-        <v>13419</v>
+        <v>11028</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2128</v>
+        <v>364</v>
       </c>
       <c r="C3" t="n">
-        <v>6357</v>
+        <v>2742</v>
       </c>
       <c r="D3" t="n">
-        <v>16482</v>
+        <v>6838</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2377</v>
+        <v>669</v>
       </c>
       <c r="C4" t="n">
-        <v>8437</v>
+        <v>3707</v>
       </c>
       <c r="D4" t="n">
-        <v>13545</v>
+        <v>6859</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1991</v>
+        <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>11024</v>
+        <v>5681</v>
       </c>
       <c r="D5" t="n">
-        <v>6347</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1062</v>
+        <v>459</v>
       </c>
       <c r="C6" t="n">
-        <v>8941</v>
+        <v>6785</v>
       </c>
       <c r="D6" t="n">
-        <v>2061</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>4863</v>
+        <v>4913</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>2107</v>
+        <v>1893</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>549</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1967</v>
+        <v>592</v>
       </c>
       <c r="C2" t="n">
-        <v>8697</v>
+        <v>10742</v>
       </c>
       <c r="D2" t="n">
-        <v>18921</v>
+        <v>10588</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1689</v>
+        <v>336</v>
       </c>
       <c r="C3" t="n">
-        <v>5464</v>
+        <v>2734</v>
       </c>
       <c r="D3" t="n">
-        <v>15110</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1995</v>
+        <v>464</v>
       </c>
       <c r="C4" t="n">
-        <v>7442</v>
+        <v>3129</v>
       </c>
       <c r="D4" t="n">
-        <v>13527</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1952</v>
+        <v>648</v>
       </c>
       <c r="C5" t="n">
-        <v>9826</v>
+        <v>4522</v>
       </c>
       <c r="D5" t="n">
-        <v>7052</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1241</v>
+        <v>546</v>
       </c>
       <c r="C6" t="n">
-        <v>9611</v>
+        <v>6172</v>
       </c>
       <c r="D6" t="n">
-        <v>2528</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>422</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>6259</v>
+        <v>5809</v>
       </c>
       <c r="D7" t="n">
-        <v>882</v>
+        <v>870</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>3018</v>
+        <v>3283</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1006</v>
+        <v>1125</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4294</v>
+        <v>5071</v>
       </c>
       <c r="C2" t="n">
-        <v>5229</v>
+        <v>5460</v>
       </c>
       <c r="D2" t="n">
-        <v>15489</v>
+        <v>7478</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1453</v>
+        <v>1006</v>
       </c>
       <c r="C2" t="n">
-        <v>5219</v>
+        <v>8250</v>
       </c>
       <c r="D2" t="n">
-        <v>14228</v>
+        <v>11181</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2261</v>
+        <v>363</v>
       </c>
       <c r="C3" t="n">
-        <v>6760</v>
+        <v>5549</v>
       </c>
       <c r="D3" t="n">
-        <v>16452</v>
+        <v>6993</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2806</v>
+        <v>354</v>
       </c>
       <c r="C4" t="n">
-        <v>10764</v>
+        <v>2848</v>
       </c>
       <c r="D4" t="n">
-        <v>13707</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1146</v>
+        <v>529</v>
       </c>
       <c r="C5" t="n">
-        <v>13854</v>
+        <v>3786</v>
       </c>
       <c r="D5" t="n">
-        <v>6273</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>389</v>
+        <v>545</v>
       </c>
       <c r="C6" t="n">
-        <v>7735</v>
+        <v>5384</v>
       </c>
       <c r="D6" t="n">
-        <v>1974</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>2957</v>
+        <v>5906</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>985</v>
+        <v>4346</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>1991</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>631</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
-        <v>88</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6805</v>
+        <v>5233</v>
       </c>
       <c r="C2" t="n">
-        <v>8471</v>
+        <v>9424</v>
       </c>
       <c r="D2" t="n">
-        <v>18250</v>
+        <v>9732</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1826</v>
+        <v>1675</v>
       </c>
       <c r="C3" t="n">
-        <v>2635</v>
+        <v>2156</v>
       </c>
       <c r="D3" t="n">
-        <v>3241</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5093</v>
+        <v>2758</v>
       </c>
       <c r="C2" t="n">
-        <v>8937</v>
+        <v>5755</v>
       </c>
       <c r="D2" t="n">
-        <v>28083</v>
+        <v>10828</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3538</v>
+        <v>2917</v>
       </c>
       <c r="C3" t="n">
-        <v>5120</v>
+        <v>5624</v>
       </c>
       <c r="D3" t="n">
-        <v>5523</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>827</v>
+        <v>800</v>
       </c>
       <c r="C4" t="n">
-        <v>1589</v>
+        <v>1392</v>
       </c>
       <c r="D4" t="n">
-        <v>1834</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4578</v>
+        <v>1991</v>
       </c>
       <c r="C2" t="n">
-        <v>5455</v>
+        <v>5031</v>
       </c>
       <c r="D2" t="n">
-        <v>25691</v>
+        <v>16889</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3533</v>
+        <v>2362</v>
       </c>
       <c r="C3" t="n">
-        <v>6233</v>
+        <v>4898</v>
       </c>
       <c r="D3" t="n">
-        <v>8734</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1850</v>
+        <v>1626</v>
       </c>
       <c r="C4" t="n">
-        <v>3555</v>
+        <v>3922</v>
       </c>
       <c r="D4" t="n">
-        <v>2486</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="5">
@@ -5179,10 +5179,10 @@
         <v>393</v>
       </c>
       <c r="C5" t="n">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="D5" t="n">
-        <v>1266</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4949</v>
+        <v>1236</v>
       </c>
       <c r="C2" t="n">
-        <v>5447</v>
+        <v>9243</v>
       </c>
       <c r="D2" t="n">
-        <v>22163</v>
+        <v>18384</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3346</v>
+        <v>1802</v>
       </c>
       <c r="C3" t="n">
-        <v>5076</v>
+        <v>4295</v>
       </c>
       <c r="D3" t="n">
-        <v>10696</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2251</v>
+        <v>1712</v>
       </c>
       <c r="C4" t="n">
-        <v>4920</v>
+        <v>4402</v>
       </c>
       <c r="D4" t="n">
-        <v>3550</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>912</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>2287</v>
+        <v>2562</v>
       </c>
       <c r="D5" t="n">
-        <v>1426</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C6" t="n">
-        <v>627</v>
+        <v>598</v>
       </c>
       <c r="D6" t="n">
-        <v>957</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5082</v>
+        <v>3187</v>
       </c>
       <c r="C2" t="n">
-        <v>8561</v>
+        <v>13960</v>
       </c>
       <c r="D2" t="n">
-        <v>21318</v>
+        <v>18461</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3000</v>
+        <v>1272</v>
       </c>
       <c r="C3" t="n">
-        <v>4313</v>
+        <v>5987</v>
       </c>
       <c r="D3" t="n">
-        <v>10995</v>
+        <v>7313</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1725</v>
+        <v>1524</v>
       </c>
       <c r="C4" t="n">
-        <v>4100</v>
+        <v>4209</v>
       </c>
       <c r="D4" t="n">
-        <v>4140</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>824</v>
+        <v>1113</v>
       </c>
       <c r="C5" t="n">
-        <v>2655</v>
+        <v>3497</v>
       </c>
       <c r="D5" t="n">
-        <v>1406</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>481</v>
       </c>
       <c r="C6" t="n">
-        <v>985</v>
+        <v>1609</v>
       </c>
       <c r="D6" t="n">
-        <v>789</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>312</v>
+        <v>446</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5556</v>
+        <v>2467</v>
       </c>
       <c r="C2" t="n">
-        <v>9629</v>
+        <v>10393</v>
       </c>
       <c r="D2" t="n">
-        <v>24274</v>
+        <v>19926</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3356</v>
+        <v>1743</v>
       </c>
       <c r="C3" t="n">
-        <v>5846</v>
+        <v>8674</v>
       </c>
       <c r="D3" t="n">
-        <v>11920</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2074</v>
+        <v>1214</v>
       </c>
       <c r="C4" t="n">
-        <v>4143</v>
+        <v>5043</v>
       </c>
       <c r="D4" t="n">
-        <v>5356</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1137</v>
+        <v>1167</v>
       </c>
       <c r="C5" t="n">
-        <v>3445</v>
+        <v>3746</v>
       </c>
       <c r="D5" t="n">
-        <v>1914</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>502</v>
+        <v>698</v>
       </c>
       <c r="C6" t="n">
-        <v>1909</v>
+        <v>2516</v>
       </c>
       <c r="D6" t="n">
-        <v>896</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>260</v>
       </c>
       <c r="C7" t="n">
-        <v>694</v>
+        <v>1004</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>271</v>
+        <v>366</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4269</v>
+        <v>2240</v>
       </c>
       <c r="C2" t="n">
-        <v>13696</v>
+        <v>6318</v>
       </c>
       <c r="D2" t="n">
-        <v>31096</v>
+        <v>15543</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3636</v>
+        <v>2252</v>
       </c>
       <c r="C3" t="n">
-        <v>6845</v>
+        <v>11968</v>
       </c>
       <c r="D3" t="n">
-        <v>13038</v>
+        <v>9413</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>1078</v>
       </c>
       <c r="C4" t="n">
-        <v>5021</v>
+        <v>6791</v>
       </c>
       <c r="D4" t="n">
-        <v>6453</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1397</v>
+        <v>644</v>
       </c>
       <c r="C5" t="n">
-        <v>3755</v>
+        <v>2465</v>
       </c>
       <c r="D5" t="n">
-        <v>2465</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>743</v>
+        <v>240</v>
       </c>
       <c r="C6" t="n">
-        <v>2698</v>
+        <v>983</v>
       </c>
       <c r="D6" t="n">
-        <v>1069</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1317</v>
+        <v>358</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>486</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
